--- a/resources/number_of_susceptibles_hun.xlsx
+++ b/resources/number_of_susceptibles_hun.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD51DE3-0976-48D8-88AA-529342FD8ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80D16D0-CFF4-4DB4-810E-16405FE436E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="320" yWindow="1620" windowWidth="18880" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="compartments" sheetId="1" r:id="rId1"/>
-    <sheet name="helper" sheetId="2" r:id="rId2"/>
-    <sheet name="Varicella" sheetId="3" r:id="rId3"/>
+    <sheet name="s0" sheetId="4" r:id="rId1"/>
+    <sheet name="compartments" sheetId="1" r:id="rId2"/>
+    <sheet name="helper" sheetId="2" r:id="rId3"/>
+    <sheet name="Varicella" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>65+</t>
   </si>
@@ -130,14 +131,20 @@
   <si>
     <t>Sum</t>
   </si>
+  <si>
+    <t>20+</t>
+  </si>
+  <si>
+    <t>s0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="#,##0;[Red]#,##0"/>
-    <numFmt numFmtId="170" formatCode="#,##0;;\-;@"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]#,##0"/>
+    <numFmt numFmtId="165" formatCode="#,##0;;\-;@"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -345,7 +352,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -364,22 +371,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -389,25 +396,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -416,7 +423,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -426,14 +433,9 @@
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -718,1720 +720,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68FD513-1C6F-464A-BDA9-97A3D7FAFCB8}">
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" style="30" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    <row r="1" spans="1:2">
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2">
         <v>96676</v>
       </c>
-      <c r="C2" s="3">
-        <f>B2</f>
-        <v>96676</v>
-      </c>
-      <c r="D2">
-        <f>ROUND(helper!M2/26,0)</f>
-        <v>53</v>
-      </c>
-      <c r="E2">
-        <f>ROUND(helper!M2/52,0)</f>
-        <v>26</v>
-      </c>
-      <c r="F2">
-        <f>ROUND(B2*helper!Q2,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="31">
-        <v>92864</v>
-      </c>
-      <c r="C3" s="3">
-        <f>B3-F3</f>
+      <c r="B3">
         <v>91425</v>
       </c>
-      <c r="D3">
-        <f>ROUND(helper!M3/26,0)</f>
-        <v>111</v>
-      </c>
-      <c r="E3">
-        <f>ROUND(helper!M3/52,0)</f>
-        <v>55</v>
-      </c>
-      <c r="F3">
-        <f>ROUND(B3*helper!Q3,0)</f>
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="31">
-        <v>95398</v>
-      </c>
-      <c r="C4" s="3">
-        <f t="shared" ref="C4:C67" si="0">B4-F4</f>
+      <c r="B4">
         <v>90914</v>
       </c>
-      <c r="D4">
-        <f>ROUND(helper!M4/26,0)</f>
-        <v>239</v>
-      </c>
-      <c r="E4">
-        <f>ROUND(helper!M4/52,0)</f>
-        <v>119</v>
-      </c>
-      <c r="F4">
-        <f>ROUND(B4*helper!Q4,0)</f>
-        <v>4484</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="31">
-        <v>97946</v>
-      </c>
-      <c r="C5" s="3">
-        <f t="shared" si="0"/>
+      <c r="B5">
         <v>87137</v>
       </c>
-      <c r="D5">
-        <f>ROUND(helper!M5/26,0)</f>
-        <v>693</v>
-      </c>
-      <c r="E5">
-        <f>ROUND(helper!M5/52,0)</f>
-        <v>347</v>
-      </c>
-      <c r="F5">
-        <f>ROUND(B5*helper!Q5,0)</f>
-        <v>10809</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="31">
-        <v>103862</v>
-      </c>
-      <c r="C6" s="3">
-        <f t="shared" si="0"/>
+      <c r="B6">
         <v>73581</v>
       </c>
-      <c r="D6">
-        <f>ROUND(helper!M6/26,0)</f>
-        <v>893</v>
-      </c>
-      <c r="E6">
-        <f>ROUND(helper!M6/52,0)</f>
-        <v>446</v>
-      </c>
-      <c r="F6">
-        <f>ROUND(B6*helper!Q6,0)</f>
-        <v>30281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="31">
-        <v>110187</v>
-      </c>
-      <c r="C7" s="3">
-        <f t="shared" si="0"/>
+      <c r="B7">
         <v>52050</v>
       </c>
-      <c r="D7">
-        <f>ROUND(helper!M7/26,0)</f>
-        <v>719</v>
-      </c>
-      <c r="E7">
-        <f>ROUND(helper!M7/52,0)</f>
-        <v>360</v>
-      </c>
-      <c r="F7">
-        <f>ROUND(B7*helper!Q7,0)</f>
-        <v>58137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="31">
-        <v>112612</v>
-      </c>
-      <c r="C8" s="3">
-        <f t="shared" si="0"/>
+      <c r="B8">
         <v>32160</v>
       </c>
-      <c r="D8">
-        <f>ROUND(helper!M8/26,0)</f>
-        <v>406</v>
-      </c>
-      <c r="E8">
-        <f>ROUND(helper!M8/52,0)</f>
-        <v>203</v>
-      </c>
-      <c r="F8">
-        <f>ROUND(B8*helper!Q8,0)</f>
-        <v>80452</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="31">
-        <v>114774</v>
-      </c>
-      <c r="C9" s="3">
-        <f t="shared" si="0"/>
+      <c r="B9">
         <v>20400</v>
       </c>
-      <c r="D9">
-        <f>ROUND(helper!M9/26,0)</f>
-        <v>166</v>
-      </c>
-      <c r="E9">
-        <f>ROUND(helper!M9/52,0)</f>
-        <v>83</v>
-      </c>
-      <c r="F9">
-        <f>ROUND(B9*helper!Q9,0)</f>
-        <v>94374</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="31">
-        <v>119484</v>
-      </c>
-      <c r="C10" s="3">
-        <f t="shared" si="0"/>
+      <c r="B10">
         <v>15711</v>
       </c>
-      <c r="D10">
-        <f>ROUND(helper!M10/26,0)</f>
-        <v>79</v>
-      </c>
-      <c r="E10">
-        <f>ROUND(helper!M10/52,0)</f>
-        <v>39</v>
-      </c>
-      <c r="F10">
-        <f>ROUND(B10*helper!Q10,0)</f>
-        <v>103773</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="31">
-        <v>124661</v>
-      </c>
-      <c r="C11" s="3">
-        <f t="shared" si="0"/>
+      <c r="B11">
         <v>13722</v>
       </c>
-      <c r="D11">
-        <f>ROUND(helper!M11/26,0)</f>
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <f>ROUND(helper!M11/52,0)</f>
-        <v>21</v>
-      </c>
-      <c r="F11">
-        <f>ROUND(B11*helper!Q11,0)</f>
-        <v>110939</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="31">
-        <v>125145</v>
-      </c>
-      <c r="C12" s="3">
-        <f t="shared" si="0"/>
-        <v>12351</v>
-      </c>
-      <c r="D12">
-        <f>ROUND(helper!M12/26,0)</f>
-        <v>27</v>
-      </c>
-      <c r="E12">
-        <f>ROUND(helper!M12/52,0)</f>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>54695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F12">
-        <f>ROUND(B12*helper!Q12,0)</f>
-        <v>112794</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="31">
-        <v>122141</v>
-      </c>
-      <c r="C13" s="3">
-        <f t="shared" si="0"/>
-        <v>11185</v>
-      </c>
-      <c r="D13">
-        <f>ROUND(helper!M13/26,0)</f>
-        <v>19</v>
-      </c>
-      <c r="E13">
-        <f>ROUND(helper!M13/52,0)</f>
-        <v>9</v>
-      </c>
-      <c r="F13">
-        <f>ROUND(B13*helper!Q13,0)</f>
-        <v>110956</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="31">
-        <v>123122</v>
-      </c>
-      <c r="C14" s="3">
-        <f t="shared" si="0"/>
-        <v>10648</v>
-      </c>
-      <c r="D14">
-        <f>ROUND(helper!M14/26,0)</f>
-        <v>14</v>
-      </c>
-      <c r="E14">
-        <f>ROUND(helper!M14/52,0)</f>
-        <v>7</v>
-      </c>
-      <c r="F14">
-        <f>ROUND(B14*helper!Q14,0)</f>
-        <v>112474</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="31">
-        <v>123987</v>
-      </c>
-      <c r="C15" s="3">
-        <f t="shared" si="0"/>
-        <v>10234</v>
-      </c>
-      <c r="D15">
-        <f>ROUND(helper!M15/26,0)</f>
-        <v>11</v>
-      </c>
-      <c r="E15">
-        <f>ROUND(helper!M15/52,0)</f>
-        <v>6</v>
-      </c>
-      <c r="F15">
-        <f>ROUND(B15*helper!Q15,0)</f>
-        <v>113753</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="31">
-        <v>129138</v>
-      </c>
-      <c r="C16" s="3">
-        <f t="shared" si="0"/>
-        <v>10277</v>
-      </c>
-      <c r="D16">
-        <f>ROUND(helper!M16/26,0)</f>
-        <v>9</v>
-      </c>
-      <c r="E16">
-        <f>ROUND(helper!M16/52,0)</f>
-        <v>5</v>
-      </c>
-      <c r="F16">
-        <f>ROUND(B16*helper!Q16,0)</f>
-        <v>118861</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="31">
-        <v>133563</v>
-      </c>
-      <c r="C17" s="3">
-        <f t="shared" si="0"/>
-        <v>10323</v>
-      </c>
-      <c r="D17">
-        <f>ROUND(helper!M17/26,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E17">
-        <f>ROUND(helper!M17/52,0)</f>
-        <v>2</v>
-      </c>
-      <c r="F17">
-        <f>ROUND(B17*helper!Q17,0)</f>
-        <v>123240</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="31">
-        <v>128051</v>
-      </c>
-      <c r="C18" s="3">
-        <f t="shared" si="0"/>
-        <v>9785</v>
-      </c>
-      <c r="D18">
-        <f>ROUND(helper!M18/26,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E18">
-        <f>ROUND(helper!M18/52,0)</f>
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <f>ROUND(B18*helper!Q18,0)</f>
-        <v>118266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="31">
-        <v>129158</v>
-      </c>
-      <c r="C19" s="3">
-        <f t="shared" si="0"/>
-        <v>9759</v>
-      </c>
-      <c r="D19">
-        <f>ROUND(helper!M19/26,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E19">
-        <f>ROUND(helper!M19/52,0)</f>
-        <v>2</v>
-      </c>
-      <c r="F19">
-        <f>ROUND(B19*helper!Q19,0)</f>
-        <v>119399</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2">
-        <v>18</v>
-      </c>
-      <c r="B20" s="31">
-        <v>134433</v>
-      </c>
-      <c r="C20" s="3">
-        <f t="shared" si="0"/>
-        <v>10047</v>
-      </c>
-      <c r="D20">
-        <f>ROUND(helper!M20/26,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E20">
-        <f>ROUND(helper!M20/52,0)</f>
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <f>ROUND(B20*helper!Q20,0)</f>
-        <v>124386</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2">
-        <v>19</v>
-      </c>
-      <c r="B21" s="31">
-        <v>143187</v>
-      </c>
-      <c r="C21" s="3">
-        <f t="shared" si="0"/>
-        <v>10585</v>
-      </c>
-      <c r="D21">
-        <f>ROUND(helper!M21/26,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E21">
-        <f>ROUND(helper!M21/52,0)</f>
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <f>ROUND(B21*helper!Q21,0)</f>
-        <v>132602</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="2">
-        <v>20</v>
-      </c>
-      <c r="B22" s="31">
-        <v>149923</v>
-      </c>
-      <c r="C22" s="3">
-        <f t="shared" si="0"/>
-        <v>10966</v>
-      </c>
-      <c r="D22">
-        <f>ROUND(helper!M22/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <f>ROUND(helper!M22/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <f>ROUND(B22*helper!Q22,0)</f>
-        <v>138957</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
-      <c r="B23" s="31">
-        <v>157094</v>
-      </c>
-      <c r="C23" s="3">
-        <f t="shared" si="0"/>
-        <v>11455</v>
-      </c>
-      <c r="D23">
-        <f>ROUND(helper!M23/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <f>ROUND(helper!M23/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <f>ROUND(B23*helper!Q23,0)</f>
-        <v>145639</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
-      <c r="B24" s="31">
-        <v>162350</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" si="0"/>
-        <v>11800</v>
-      </c>
-      <c r="D24">
-        <f>ROUND(helper!M24/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <f>ROUND(helper!M24/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <f>ROUND(B24*helper!Q24,0)</f>
-        <v>150550</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
-      <c r="B25" s="31">
-        <v>168002</v>
-      </c>
-      <c r="C25" s="3">
-        <f t="shared" si="0"/>
-        <v>12171</v>
-      </c>
-      <c r="D25">
-        <f>ROUND(helper!M25/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <f>ROUND(helper!M25/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <f>ROUND(B25*helper!Q25,0)</f>
-        <v>155831</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" s="31">
-        <v>174358</v>
-      </c>
-      <c r="C26" s="3">
-        <f t="shared" si="0"/>
-        <v>12590</v>
-      </c>
-      <c r="D26">
-        <f>ROUND(helper!M26/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <f>ROUND(helper!M26/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <f>ROUND(B26*helper!Q26,0)</f>
-        <v>161768</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2">
-        <v>25</v>
-      </c>
-      <c r="B27" s="31">
-        <v>181044</v>
-      </c>
-      <c r="C27" s="3">
-        <f t="shared" si="0"/>
-        <v>13029</v>
-      </c>
-      <c r="D27">
-        <f>ROUND(helper!M27/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <f>ROUND(helper!M27/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <f>ROUND(B27*helper!Q27,0)</f>
-        <v>168015</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="2">
-        <v>26</v>
-      </c>
-      <c r="B28" s="31">
-        <v>172946</v>
-      </c>
-      <c r="C28" s="3">
-        <f t="shared" si="0"/>
-        <v>12405</v>
-      </c>
-      <c r="D28">
-        <f>ROUND(helper!M28/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <f>ROUND(helper!M28/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <f>ROUND(B28*helper!Q28,0)</f>
-        <v>160541</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="2">
-        <v>27</v>
-      </c>
-      <c r="B29" s="31">
-        <v>145417</v>
-      </c>
-      <c r="C29" s="3">
-        <f t="shared" si="0"/>
-        <v>10396</v>
-      </c>
-      <c r="D29">
-        <f>ROUND(helper!M29/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <f>ROUND(helper!M29/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <f>ROUND(B29*helper!Q29,0)</f>
-        <v>135021</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="2">
-        <v>28</v>
-      </c>
-      <c r="B30" s="31">
-        <v>144654</v>
-      </c>
-      <c r="C30" s="3">
-        <f t="shared" si="0"/>
-        <v>10306</v>
-      </c>
-      <c r="D30">
-        <f>ROUND(helper!M30/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <f>ROUND(helper!M30/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <f>ROUND(B30*helper!Q30,0)</f>
-        <v>134348</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="2">
-        <v>29</v>
-      </c>
-      <c r="B31" s="31">
-        <v>141084</v>
-      </c>
-      <c r="C31" s="3">
-        <f t="shared" si="0"/>
-        <v>10018</v>
-      </c>
-      <c r="D31">
-        <f>ROUND(helper!M31/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E31">
-        <f>ROUND(helper!M31/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <f>ROUND(B31*helper!Q31,0)</f>
-        <v>131066</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="2">
-        <v>30</v>
-      </c>
-      <c r="B32" s="31">
-        <v>145705</v>
-      </c>
-      <c r="C32" s="3">
-        <f t="shared" si="0"/>
-        <v>10313</v>
-      </c>
-      <c r="D32">
-        <f>ROUND(helper!M32/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <f>ROUND(helper!M32/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <f>ROUND(B32*helper!Q32,0)</f>
-        <v>135392</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="2">
+      <c r="B13">
+        <v>668392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="31">
-        <v>143953</v>
-      </c>
-      <c r="C33" s="3">
-        <f t="shared" si="0"/>
-        <v>10158</v>
-      </c>
-      <c r="D33">
-        <f>ROUND(helper!M33/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <f>ROUND(helper!M33/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <f>ROUND(B33*helper!Q33,0)</f>
-        <v>133795</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="2">
-        <v>32</v>
-      </c>
-      <c r="B34" s="31">
-        <v>145194</v>
-      </c>
-      <c r="C34" s="3">
-        <f t="shared" si="0"/>
-        <v>10216</v>
-      </c>
-      <c r="D34">
-        <f>ROUND(helper!M34/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <f>ROUND(helper!M34/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <f>ROUND(B34*helper!Q34,0)</f>
-        <v>134978</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="2">
-        <v>33</v>
-      </c>
-      <c r="B35" s="31">
-        <v>139103</v>
-      </c>
-      <c r="C35" s="3">
-        <f t="shared" si="0"/>
-        <v>9760</v>
-      </c>
-      <c r="D35">
-        <f>ROUND(helper!M35/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <f>ROUND(helper!M35/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <f>ROUND(B35*helper!Q35,0)</f>
-        <v>129343</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="2">
-        <v>34</v>
-      </c>
-      <c r="B36" s="31">
-        <v>127404</v>
-      </c>
-      <c r="C36" s="3">
-        <f t="shared" si="0"/>
-        <v>8916</v>
-      </c>
-      <c r="D36">
-        <f>ROUND(helper!M36/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <f>ROUND(helper!M36/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <f>ROUND(B36*helper!Q36,0)</f>
-        <v>118488</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="2">
-        <v>35</v>
-      </c>
-      <c r="B37" s="31">
-        <v>123682</v>
-      </c>
-      <c r="C37" s="3">
-        <f t="shared" si="0"/>
-        <v>8634</v>
-      </c>
-      <c r="D37">
-        <f>ROUND(helper!M37/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <f>ROUND(helper!M37/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <f>ROUND(B37*helper!Q37,0)</f>
-        <v>115048</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="2">
-        <v>36</v>
-      </c>
-      <c r="B38" s="31">
-        <v>121535</v>
-      </c>
-      <c r="C38" s="3">
-        <f t="shared" si="0"/>
-        <v>8464</v>
-      </c>
-      <c r="D38">
-        <f>ROUND(helper!M38/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <f>ROUND(helper!M38/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <f>ROUND(B38*helper!Q38,0)</f>
-        <v>113071</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="2">
-        <v>37</v>
-      </c>
-      <c r="B39" s="31">
-        <v>121246</v>
-      </c>
-      <c r="C39" s="3">
-        <f t="shared" si="0"/>
-        <v>8425</v>
-      </c>
-      <c r="D39">
-        <f>ROUND(helper!M39/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <f>ROUND(helper!M39/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <f>ROUND(B39*helper!Q39,0)</f>
-        <v>112821</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="2">
-        <v>38</v>
-      </c>
-      <c r="B40" s="31">
-        <v>118489</v>
-      </c>
-      <c r="C40" s="3">
-        <f t="shared" si="0"/>
-        <v>8212</v>
-      </c>
-      <c r="D40">
-        <f>ROUND(helper!M40/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <f>ROUND(helper!M40/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <f>ROUND(B40*helper!Q40,0)</f>
-        <v>110277</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2">
-        <v>39</v>
-      </c>
-      <c r="B41" s="31">
-        <v>125874</v>
-      </c>
-      <c r="C41" s="3">
-        <f t="shared" si="0"/>
-        <v>8699</v>
-      </c>
-      <c r="D41">
-        <f>ROUND(helper!M41/26,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E41">
-        <f>ROUND(helper!M41/52,0)</f>
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <f>ROUND(B41*helper!Q41,0)</f>
-        <v>117175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="2">
-        <v>40</v>
-      </c>
-      <c r="B42" s="31">
-        <v>133418</v>
-      </c>
-      <c r="C42" s="3">
-        <f t="shared" si="0"/>
-        <v>9193</v>
-      </c>
-      <c r="D42">
-        <f>ROUND(helper!M42/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <f>ROUND(helper!M42/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <f>ROUND(B42*helper!Q42,0)</f>
-        <v>124225</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="2">
-        <v>41</v>
-      </c>
-      <c r="B43" s="31">
-        <v>132255</v>
-      </c>
-      <c r="C43" s="3">
-        <f t="shared" si="0"/>
-        <v>9103</v>
-      </c>
-      <c r="D43">
-        <f>ROUND(helper!M43/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <f>ROUND(helper!M43/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <f>ROUND(B43*helper!Q43,0)</f>
-        <v>123152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="2">
-        <v>42</v>
-      </c>
-      <c r="B44" s="31">
-        <v>139181</v>
-      </c>
-      <c r="C44" s="3">
-        <f t="shared" si="0"/>
-        <v>9571</v>
-      </c>
-      <c r="D44">
-        <f>ROUND(helper!M44/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <f>ROUND(helper!M44/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <f>ROUND(B44*helper!Q44,0)</f>
-        <v>129610</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="2">
-        <v>43</v>
-      </c>
-      <c r="B45" s="31">
-        <v>143915</v>
-      </c>
-      <c r="C45" s="3">
-        <f t="shared" si="0"/>
-        <v>9887</v>
-      </c>
-      <c r="D45">
-        <f>ROUND(helper!M45/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <f>ROUND(helper!M45/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <f>ROUND(B45*helper!Q45,0)</f>
-        <v>134028</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="2">
-        <v>44</v>
-      </c>
-      <c r="B46" s="31">
-        <v>164044</v>
-      </c>
-      <c r="C46" s="3">
-        <f t="shared" si="0"/>
-        <v>11259</v>
-      </c>
-      <c r="D46">
-        <f>ROUND(helper!M46/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <f>ROUND(helper!M46/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <f>ROUND(B46*helper!Q46,0)</f>
-        <v>152785</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="2">
-        <v>45</v>
-      </c>
-      <c r="B47" s="31">
-        <v>175165</v>
-      </c>
-      <c r="C47" s="3">
-        <f t="shared" si="0"/>
-        <v>12010</v>
-      </c>
-      <c r="D47">
-        <f>ROUND(helper!M47/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <f>ROUND(helper!M47/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <f>ROUND(B47*helper!Q47,0)</f>
-        <v>163155</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="2">
-        <v>46</v>
-      </c>
-      <c r="B48" s="31">
-        <v>183711</v>
-      </c>
-      <c r="C48" s="3">
-        <f t="shared" si="0"/>
-        <v>12581</v>
-      </c>
-      <c r="D48">
-        <f>ROUND(helper!M48/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E48">
-        <f>ROUND(helper!M48/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <f>ROUND(B48*helper!Q48,0)</f>
-        <v>171130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="2">
-        <v>47</v>
-      </c>
-      <c r="B49" s="31">
-        <v>167115</v>
-      </c>
-      <c r="C49" s="3">
-        <f t="shared" si="0"/>
-        <v>11432</v>
-      </c>
-      <c r="D49">
-        <f>ROUND(helper!M49/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <f>ROUND(helper!M49/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <f>ROUND(B49*helper!Q49,0)</f>
-        <v>155683</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="2">
-        <v>48</v>
-      </c>
-      <c r="B50" s="31">
-        <v>149758</v>
-      </c>
-      <c r="C50" s="3">
-        <f t="shared" si="0"/>
-        <v>10232</v>
-      </c>
-      <c r="D50">
-        <f>ROUND(helper!M50/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <f>ROUND(helper!M50/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <f>ROUND(B50*helper!Q50,0)</f>
-        <v>139526</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="2">
-        <v>49</v>
-      </c>
-      <c r="B51" s="31">
-        <v>150679</v>
-      </c>
-      <c r="C51" s="3">
-        <f t="shared" si="0"/>
-        <v>10283</v>
-      </c>
-      <c r="D51">
-        <f>ROUND(helper!M51/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <f>ROUND(helper!M51/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <f>ROUND(B51*helper!Q51,0)</f>
-        <v>140396</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="2">
-        <v>50</v>
-      </c>
-      <c r="B52" s="31">
-        <v>154879</v>
-      </c>
-      <c r="C52" s="3">
-        <f t="shared" si="0"/>
-        <v>10557</v>
-      </c>
-      <c r="D52">
-        <f>ROUND(helper!M52/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <f>ROUND(helper!M52/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <f>ROUND(B52*helper!Q52,0)</f>
-        <v>144322</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="2">
-        <v>51</v>
-      </c>
-      <c r="B53" s="31">
-        <v>146276</v>
-      </c>
-      <c r="C53" s="3">
-        <f t="shared" si="0"/>
-        <v>9967</v>
-      </c>
-      <c r="D53">
-        <f>ROUND(helper!M53/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <f>ROUND(helper!M53/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <f>ROUND(B53*helper!Q53,0)</f>
-        <v>136309</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="2">
-        <v>52</v>
-      </c>
-      <c r="B54" s="31">
-        <v>143578</v>
-      </c>
-      <c r="C54" s="3">
-        <f t="shared" si="0"/>
-        <v>9781</v>
-      </c>
-      <c r="D54">
-        <f>ROUND(helper!M54/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <f>ROUND(helper!M54/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <f>ROUND(B54*helper!Q54,0)</f>
-        <v>133797</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="2">
-        <v>53</v>
-      </c>
-      <c r="B55" s="31">
-        <v>137180</v>
-      </c>
-      <c r="C55" s="3">
-        <f t="shared" si="0"/>
-        <v>9342</v>
-      </c>
-      <c r="D55">
-        <f>ROUND(helper!M55/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <f>ROUND(helper!M55/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <f>ROUND(B55*helper!Q55,0)</f>
-        <v>127838</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="2">
-        <v>54</v>
-      </c>
-      <c r="B56" s="31">
-        <v>120058</v>
-      </c>
-      <c r="C56" s="3">
-        <f t="shared" si="0"/>
-        <v>8174</v>
-      </c>
-      <c r="D56">
-        <f>ROUND(helper!M56/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <f>ROUND(helper!M56/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <f>ROUND(B56*helper!Q56,0)</f>
-        <v>111884</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="2">
-        <v>55</v>
-      </c>
-      <c r="B57" s="31">
-        <v>117801</v>
-      </c>
-      <c r="C57" s="3">
-        <f t="shared" si="0"/>
-        <v>8019</v>
-      </c>
-      <c r="D57">
-        <f>ROUND(helper!M57/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <f>ROUND(helper!M57/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <f>ROUND(B57*helper!Q57,0)</f>
-        <v>109782</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="2">
-        <v>56</v>
-      </c>
-      <c r="B58" s="31">
-        <v>132714</v>
-      </c>
-      <c r="C58" s="3">
-        <f t="shared" si="0"/>
-        <v>9032</v>
-      </c>
-      <c r="D58">
-        <f>ROUND(helper!M58/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <f>ROUND(helper!M58/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <f>ROUND(B58*helper!Q58,0)</f>
-        <v>123682</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="2">
-        <v>57</v>
-      </c>
-      <c r="B59" s="31">
-        <v>121511</v>
-      </c>
-      <c r="C59" s="3">
-        <f t="shared" si="0"/>
-        <v>8268</v>
-      </c>
-      <c r="D59">
-        <f>ROUND(helper!M59/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <f>ROUND(helper!M59/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <f>ROUND(B59*helper!Q59,0)</f>
-        <v>113243</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="2">
-        <v>58</v>
-      </c>
-      <c r="B60" s="31">
-        <v>123909</v>
-      </c>
-      <c r="C60" s="3">
-        <f t="shared" si="0"/>
-        <v>8429</v>
-      </c>
-      <c r="D60">
-        <f>ROUND(helper!M60/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <f>ROUND(helper!M60/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <f>ROUND(B60*helper!Q60,0)</f>
-        <v>115480</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="2">
-        <v>59</v>
-      </c>
-      <c r="B61" s="31">
-        <v>114481</v>
-      </c>
-      <c r="C61" s="3">
-        <f t="shared" si="0"/>
-        <v>7786</v>
-      </c>
-      <c r="D61">
-        <f>ROUND(helper!M61/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <f>ROUND(helper!M61/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <f>ROUND(B61*helper!Q61,0)</f>
-        <v>106695</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="2">
-        <v>60</v>
-      </c>
-      <c r="B62" s="31">
-        <v>117860</v>
-      </c>
-      <c r="C62" s="3">
-        <f t="shared" si="0"/>
-        <v>8013</v>
-      </c>
-      <c r="D62">
-        <f>ROUND(helper!M62/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E62">
-        <f>ROUND(helper!M62/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <f>ROUND(B62*helper!Q62,0)</f>
-        <v>109847</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="2">
-        <v>61</v>
-      </c>
-      <c r="B63" s="31">
-        <v>108190</v>
-      </c>
-      <c r="C63" s="3">
-        <f t="shared" si="0"/>
-        <v>7355</v>
-      </c>
-      <c r="D63">
-        <f>ROUND(helper!M63/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <f>ROUND(helper!M63/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <f>ROUND(B63*helper!Q63,0)</f>
-        <v>100835</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="2">
-        <v>62</v>
-      </c>
-      <c r="B64" s="31">
-        <v>106387</v>
-      </c>
-      <c r="C64" s="3">
-        <f t="shared" si="0"/>
-        <v>7231</v>
-      </c>
-      <c r="D64">
-        <f>ROUND(helper!M64/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E64">
-        <f>ROUND(helper!M64/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <f>ROUND(B64*helper!Q64,0)</f>
-        <v>99156</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="2">
-        <v>63</v>
-      </c>
-      <c r="B65" s="31">
-        <v>102165</v>
-      </c>
-      <c r="C65" s="3">
-        <f t="shared" si="0"/>
-        <v>6943</v>
-      </c>
-      <c r="D65">
-        <f>ROUND(helper!M65/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <f>ROUND(helper!M65/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <f>ROUND(B65*helper!Q65,0)</f>
-        <v>95222</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="2">
-        <v>64</v>
-      </c>
-      <c r="B66" s="31">
-        <v>99642</v>
-      </c>
-      <c r="C66" s="3">
-        <f t="shared" si="0"/>
-        <v>6771</v>
-      </c>
-      <c r="D66">
-        <f>ROUND(helper!M66/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <f>ROUND(helper!M66/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <f>ROUND(B66*helper!Q66,0)</f>
-        <v>92871</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="32">
-        <v>1544980</v>
-      </c>
-      <c r="C67" s="3">
-        <f t="shared" si="0"/>
-        <v>104964</v>
-      </c>
-      <c r="D67">
-        <f>ROUND(helper!M67/26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <f>ROUND(helper!M67/52,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <f>ROUND(B67*helper!Q67,0)</f>
-        <v>1440016</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B68" s="33">
-        <f>SUM(B2:B67)</f>
-        <v>10200298</v>
-      </c>
-      <c r="C68" s="33">
-        <f t="shared" ref="C68:F68" si="1">SUM(C2:C67)</f>
-        <v>1222086</v>
-      </c>
-      <c r="D68" s="33">
-        <f t="shared" si="1"/>
-        <v>3521</v>
-      </c>
-      <c r="E68" s="33">
-        <f t="shared" si="1"/>
-        <v>1769</v>
-      </c>
-      <c r="F68" s="33">
-        <f t="shared" si="1"/>
-        <v>8978212</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="2"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="2"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="2"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="2"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="2"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="2"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="2"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="2"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="2"/>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" s="2"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="2"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="2"/>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2"/>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="2"/>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="2"/>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="2"/>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="2"/>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="2"/>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="2"/>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="2"/>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="2"/>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="2"/>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="2"/>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="2"/>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="2"/>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="2"/>
+      <c r="B14">
+        <v>7681349</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2439,6 +839,1735 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G94"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="5.26953125" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="30">
+        <v>96676</v>
+      </c>
+      <c r="C2" s="3">
+        <f>B2</f>
+        <v>96676</v>
+      </c>
+      <c r="D2">
+        <f>ROUND(helper!M2/26,0)</f>
+        <v>53</v>
+      </c>
+      <c r="E2">
+        <f>ROUND(helper!M2/52,0)</f>
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <f>ROUND(B2*helper!Q2,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="30">
+        <v>92864</v>
+      </c>
+      <c r="C3" s="3">
+        <f>B3-F3</f>
+        <v>91425</v>
+      </c>
+      <c r="D3">
+        <f>ROUND(helper!M3/26,0)</f>
+        <v>111</v>
+      </c>
+      <c r="E3">
+        <f>ROUND(helper!M3/52,0)</f>
+        <v>55</v>
+      </c>
+      <c r="F3">
+        <f>ROUND(B3*helper!Q3,0)</f>
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="30">
+        <v>95398</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" ref="C4:C67" si="0">B4-F4</f>
+        <v>90914</v>
+      </c>
+      <c r="D4">
+        <f>ROUND(helper!M4/26,0)</f>
+        <v>239</v>
+      </c>
+      <c r="E4">
+        <f>ROUND(helper!M4/52,0)</f>
+        <v>119</v>
+      </c>
+      <c r="F4">
+        <f>ROUND(B4*helper!Q4,0)</f>
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="30">
+        <v>97946</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="0"/>
+        <v>87137</v>
+      </c>
+      <c r="D5">
+        <f>ROUND(helper!M5/26,0)</f>
+        <v>693</v>
+      </c>
+      <c r="E5">
+        <f>ROUND(helper!M5/52,0)</f>
+        <v>347</v>
+      </c>
+      <c r="F5">
+        <f>ROUND(B5*helper!Q5,0)</f>
+        <v>10809</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="30">
+        <v>103862</v>
+      </c>
+      <c r="C6" s="3">
+        <f t="shared" si="0"/>
+        <v>73581</v>
+      </c>
+      <c r="D6">
+        <f>ROUND(helper!M6/26,0)</f>
+        <v>893</v>
+      </c>
+      <c r="E6">
+        <f>ROUND(helper!M6/52,0)</f>
+        <v>446</v>
+      </c>
+      <c r="F6">
+        <f>ROUND(B6*helper!Q6,0)</f>
+        <v>30281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="30">
+        <v>110187</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="0"/>
+        <v>52050</v>
+      </c>
+      <c r="D7">
+        <f>ROUND(helper!M7/26,0)</f>
+        <v>719</v>
+      </c>
+      <c r="E7">
+        <f>ROUND(helper!M7/52,0)</f>
+        <v>360</v>
+      </c>
+      <c r="F7">
+        <f>ROUND(B7*helper!Q7,0)</f>
+        <v>58137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="30">
+        <v>112612</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="0"/>
+        <v>32160</v>
+      </c>
+      <c r="D8">
+        <f>ROUND(helper!M8/26,0)</f>
+        <v>406</v>
+      </c>
+      <c r="E8">
+        <f>ROUND(helper!M8/52,0)</f>
+        <v>203</v>
+      </c>
+      <c r="F8">
+        <f>ROUND(B8*helper!Q8,0)</f>
+        <v>80452</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="30">
+        <v>114774</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" si="0"/>
+        <v>20400</v>
+      </c>
+      <c r="D9">
+        <f>ROUND(helper!M9/26,0)</f>
+        <v>166</v>
+      </c>
+      <c r="E9">
+        <f>ROUND(helper!M9/52,0)</f>
+        <v>83</v>
+      </c>
+      <c r="F9">
+        <f>ROUND(B9*helper!Q9,0)</f>
+        <v>94374</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="30">
+        <v>119484</v>
+      </c>
+      <c r="C10" s="3">
+        <f t="shared" si="0"/>
+        <v>15711</v>
+      </c>
+      <c r="D10">
+        <f>ROUND(helper!M10/26,0)</f>
+        <v>79</v>
+      </c>
+      <c r="E10">
+        <f>ROUND(helper!M10/52,0)</f>
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <f>ROUND(B10*helper!Q10,0)</f>
+        <v>103773</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="30">
+        <v>124661</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" si="0"/>
+        <v>13722</v>
+      </c>
+      <c r="D11">
+        <f>ROUND(helper!M11/26,0)</f>
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <f>ROUND(helper!M11/52,0)</f>
+        <v>21</v>
+      </c>
+      <c r="F11">
+        <f>ROUND(B11*helper!Q11,0)</f>
+        <v>110939</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="30">
+        <v>125145</v>
+      </c>
+      <c r="C12" s="3">
+        <f t="shared" si="0"/>
+        <v>12351</v>
+      </c>
+      <c r="D12">
+        <f>ROUND(helper!M12/26,0)</f>
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <f>ROUND(helper!M12/52,0)</f>
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <f>ROUND(B12*helper!Q12,0)</f>
+        <v>112794</v>
+      </c>
+      <c r="G12" s="3">
+        <f>SUM(C12:C16)</f>
+        <v>54695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="30">
+        <v>122141</v>
+      </c>
+      <c r="C13" s="3">
+        <f t="shared" si="0"/>
+        <v>11185</v>
+      </c>
+      <c r="D13">
+        <f>ROUND(helper!M13/26,0)</f>
+        <v>19</v>
+      </c>
+      <c r="E13">
+        <f>ROUND(helper!M13/52,0)</f>
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <f>ROUND(B13*helper!Q13,0)</f>
+        <v>110956</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="30">
+        <v>123122</v>
+      </c>
+      <c r="C14" s="3">
+        <f t="shared" si="0"/>
+        <v>10648</v>
+      </c>
+      <c r="D14">
+        <f>ROUND(helper!M14/26,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <f>ROUND(helper!M14/52,0)</f>
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <f>ROUND(B14*helper!Q14,0)</f>
+        <v>112474</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="30">
+        <v>123987</v>
+      </c>
+      <c r="C15" s="3">
+        <f t="shared" si="0"/>
+        <v>10234</v>
+      </c>
+      <c r="D15">
+        <f>ROUND(helper!M15/26,0)</f>
+        <v>11</v>
+      </c>
+      <c r="E15">
+        <f>ROUND(helper!M15/52,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <f>ROUND(B15*helper!Q15,0)</f>
+        <v>113753</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="30">
+        <v>129138</v>
+      </c>
+      <c r="C16" s="3">
+        <f t="shared" si="0"/>
+        <v>10277</v>
+      </c>
+      <c r="D16">
+        <f>ROUND(helper!M16/26,0)</f>
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <f>ROUND(helper!M16/52,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <f>ROUND(B16*helper!Q16,0)</f>
+        <v>118861</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="30">
+        <v>133563</v>
+      </c>
+      <c r="C17" s="3">
+        <f t="shared" si="0"/>
+        <v>10323</v>
+      </c>
+      <c r="D17">
+        <f>ROUND(helper!M17/26,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <f>ROUND(helper!M17/52,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <f>ROUND(B17*helper!Q17,0)</f>
+        <v>123240</v>
+      </c>
+      <c r="G17" s="3">
+        <f>SUM(B17:B21)</f>
+        <v>668392</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="30">
+        <v>128051</v>
+      </c>
+      <c r="C18" s="3">
+        <f t="shared" si="0"/>
+        <v>9785</v>
+      </c>
+      <c r="D18">
+        <f>ROUND(helper!M18/26,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <f>ROUND(helper!M18/52,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <f>ROUND(B18*helper!Q18,0)</f>
+        <v>118266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="30">
+        <v>129158</v>
+      </c>
+      <c r="C19" s="3">
+        <f t="shared" si="0"/>
+        <v>9759</v>
+      </c>
+      <c r="D19">
+        <f>ROUND(helper!M19/26,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <f>ROUND(helper!M19/52,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <f>ROUND(B19*helper!Q19,0)</f>
+        <v>119399</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="30">
+        <v>134433</v>
+      </c>
+      <c r="C20" s="3">
+        <f t="shared" si="0"/>
+        <v>10047</v>
+      </c>
+      <c r="D20">
+        <f>ROUND(helper!M20/26,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <f>ROUND(helper!M20/52,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <f>ROUND(B20*helper!Q20,0)</f>
+        <v>124386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="30">
+        <v>143187</v>
+      </c>
+      <c r="C21" s="3">
+        <f t="shared" si="0"/>
+        <v>10585</v>
+      </c>
+      <c r="D21">
+        <f>ROUND(helper!M21/26,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <f>ROUND(helper!M21/52,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <f>ROUND(B21*helper!Q21,0)</f>
+        <v>132602</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="30">
+        <v>149923</v>
+      </c>
+      <c r="C22" s="3">
+        <f t="shared" si="0"/>
+        <v>10966</v>
+      </c>
+      <c r="D22">
+        <f>ROUND(helper!M22/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <f>ROUND(helper!M22/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <f>ROUND(B22*helper!Q22,0)</f>
+        <v>138957</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="30">
+        <v>157094</v>
+      </c>
+      <c r="C23" s="3">
+        <f t="shared" si="0"/>
+        <v>11455</v>
+      </c>
+      <c r="D23">
+        <f>ROUND(helper!M23/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <f>ROUND(helper!M23/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <f>ROUND(B23*helper!Q23,0)</f>
+        <v>145639</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="30">
+        <v>162350</v>
+      </c>
+      <c r="C24" s="3">
+        <f t="shared" si="0"/>
+        <v>11800</v>
+      </c>
+      <c r="D24">
+        <f>ROUND(helper!M24/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f>ROUND(helper!M24/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <f>ROUND(B24*helper!Q24,0)</f>
+        <v>150550</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="30">
+        <v>168002</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" si="0"/>
+        <v>12171</v>
+      </c>
+      <c r="D25">
+        <f>ROUND(helper!M25/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <f>ROUND(helper!M25/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <f>ROUND(B25*helper!Q25,0)</f>
+        <v>155831</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="30">
+        <v>174358</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="0"/>
+        <v>12590</v>
+      </c>
+      <c r="D26">
+        <f>ROUND(helper!M26/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <f>ROUND(helper!M26/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <f>ROUND(B26*helper!Q26,0)</f>
+        <v>161768</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="30">
+        <v>181044</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="0"/>
+        <v>13029</v>
+      </c>
+      <c r="D27">
+        <f>ROUND(helper!M27/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <f>ROUND(helper!M27/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <f>ROUND(B27*helper!Q27,0)</f>
+        <v>168015</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="30">
+        <v>172946</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" si="0"/>
+        <v>12405</v>
+      </c>
+      <c r="D28">
+        <f>ROUND(helper!M28/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <f>ROUND(helper!M28/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <f>ROUND(B28*helper!Q28,0)</f>
+        <v>160541</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="30">
+        <v>145417</v>
+      </c>
+      <c r="C29" s="3">
+        <f t="shared" si="0"/>
+        <v>10396</v>
+      </c>
+      <c r="D29">
+        <f>ROUND(helper!M29/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <f>ROUND(helper!M29/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <f>ROUND(B29*helper!Q29,0)</f>
+        <v>135021</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="30">
+        <v>144654</v>
+      </c>
+      <c r="C30" s="3">
+        <f t="shared" si="0"/>
+        <v>10306</v>
+      </c>
+      <c r="D30">
+        <f>ROUND(helper!M30/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <f>ROUND(helper!M30/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <f>ROUND(B30*helper!Q30,0)</f>
+        <v>134348</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="30">
+        <v>141084</v>
+      </c>
+      <c r="C31" s="3">
+        <f t="shared" si="0"/>
+        <v>10018</v>
+      </c>
+      <c r="D31">
+        <f>ROUND(helper!M31/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <f>ROUND(helper!M31/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <f>ROUND(B31*helper!Q31,0)</f>
+        <v>131066</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="30">
+        <v>145705</v>
+      </c>
+      <c r="C32" s="3">
+        <f t="shared" si="0"/>
+        <v>10313</v>
+      </c>
+      <c r="D32">
+        <f>ROUND(helper!M32/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <f>ROUND(helper!M32/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <f>ROUND(B32*helper!Q32,0)</f>
+        <v>135392</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="30">
+        <v>143953</v>
+      </c>
+      <c r="C33" s="3">
+        <f t="shared" si="0"/>
+        <v>10158</v>
+      </c>
+      <c r="D33">
+        <f>ROUND(helper!M33/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <f>ROUND(helper!M33/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <f>ROUND(B33*helper!Q33,0)</f>
+        <v>133795</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="30">
+        <v>145194</v>
+      </c>
+      <c r="C34" s="3">
+        <f t="shared" si="0"/>
+        <v>10216</v>
+      </c>
+      <c r="D34">
+        <f>ROUND(helper!M34/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <f>ROUND(helper!M34/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <f>ROUND(B34*helper!Q34,0)</f>
+        <v>134978</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="30">
+        <v>139103</v>
+      </c>
+      <c r="C35" s="3">
+        <f t="shared" si="0"/>
+        <v>9760</v>
+      </c>
+      <c r="D35">
+        <f>ROUND(helper!M35/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <f>ROUND(helper!M35/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <f>ROUND(B35*helper!Q35,0)</f>
+        <v>129343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="30">
+        <v>127404</v>
+      </c>
+      <c r="C36" s="3">
+        <f t="shared" si="0"/>
+        <v>8916</v>
+      </c>
+      <c r="D36">
+        <f>ROUND(helper!M36/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <f>ROUND(helper!M36/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <f>ROUND(B36*helper!Q36,0)</f>
+        <v>118488</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="2">
+        <v>35</v>
+      </c>
+      <c r="B37" s="30">
+        <v>123682</v>
+      </c>
+      <c r="C37" s="3">
+        <f t="shared" si="0"/>
+        <v>8634</v>
+      </c>
+      <c r="D37">
+        <f>ROUND(helper!M37/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <f>ROUND(helper!M37/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <f>ROUND(B37*helper!Q37,0)</f>
+        <v>115048</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" s="30">
+        <v>121535</v>
+      </c>
+      <c r="C38" s="3">
+        <f t="shared" si="0"/>
+        <v>8464</v>
+      </c>
+      <c r="D38">
+        <f>ROUND(helper!M38/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <f>ROUND(helper!M38/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <f>ROUND(B38*helper!Q38,0)</f>
+        <v>113071</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="2">
+        <v>37</v>
+      </c>
+      <c r="B39" s="30">
+        <v>121246</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" si="0"/>
+        <v>8425</v>
+      </c>
+      <c r="D39">
+        <f>ROUND(helper!M39/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <f>ROUND(helper!M39/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <f>ROUND(B39*helper!Q39,0)</f>
+        <v>112821</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="30">
+        <v>118489</v>
+      </c>
+      <c r="C40" s="3">
+        <f t="shared" si="0"/>
+        <v>8212</v>
+      </c>
+      <c r="D40">
+        <f>ROUND(helper!M40/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <f>ROUND(helper!M40/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <f>ROUND(B40*helper!Q40,0)</f>
+        <v>110277</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="30">
+        <v>125874</v>
+      </c>
+      <c r="C41" s="3">
+        <f t="shared" si="0"/>
+        <v>8699</v>
+      </c>
+      <c r="D41">
+        <f>ROUND(helper!M41/26,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <f>ROUND(helper!M41/52,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <f>ROUND(B41*helper!Q41,0)</f>
+        <v>117175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="30">
+        <v>133418</v>
+      </c>
+      <c r="C42" s="3">
+        <f t="shared" si="0"/>
+        <v>9193</v>
+      </c>
+      <c r="D42">
+        <f>ROUND(helper!M42/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <f>ROUND(helper!M42/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <f>ROUND(B42*helper!Q42,0)</f>
+        <v>124225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" s="30">
+        <v>132255</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" si="0"/>
+        <v>9103</v>
+      </c>
+      <c r="D43">
+        <f>ROUND(helper!M43/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <f>ROUND(helper!M43/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <f>ROUND(B43*helper!Q43,0)</f>
+        <v>123152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="30">
+        <v>139181</v>
+      </c>
+      <c r="C44" s="3">
+        <f t="shared" si="0"/>
+        <v>9571</v>
+      </c>
+      <c r="D44">
+        <f>ROUND(helper!M44/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <f>ROUND(helper!M44/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <f>ROUND(B44*helper!Q44,0)</f>
+        <v>129610</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="30">
+        <v>143915</v>
+      </c>
+      <c r="C45" s="3">
+        <f t="shared" si="0"/>
+        <v>9887</v>
+      </c>
+      <c r="D45">
+        <f>ROUND(helper!M45/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <f>ROUND(helper!M45/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <f>ROUND(B45*helper!Q45,0)</f>
+        <v>134028</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="30">
+        <v>164044</v>
+      </c>
+      <c r="C46" s="3">
+        <f t="shared" si="0"/>
+        <v>11259</v>
+      </c>
+      <c r="D46">
+        <f>ROUND(helper!M46/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <f>ROUND(helper!M46/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <f>ROUND(B46*helper!Q46,0)</f>
+        <v>152785</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="30">
+        <v>175165</v>
+      </c>
+      <c r="C47" s="3">
+        <f t="shared" si="0"/>
+        <v>12010</v>
+      </c>
+      <c r="D47">
+        <f>ROUND(helper!M47/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <f>ROUND(helper!M47/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <f>ROUND(B47*helper!Q47,0)</f>
+        <v>163155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" s="30">
+        <v>183711</v>
+      </c>
+      <c r="C48" s="3">
+        <f t="shared" si="0"/>
+        <v>12581</v>
+      </c>
+      <c r="D48">
+        <f>ROUND(helper!M48/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <f>ROUND(helper!M48/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <f>ROUND(B48*helper!Q48,0)</f>
+        <v>171130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" s="30">
+        <v>167115</v>
+      </c>
+      <c r="C49" s="3">
+        <f t="shared" si="0"/>
+        <v>11432</v>
+      </c>
+      <c r="D49">
+        <f>ROUND(helper!M49/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <f>ROUND(helper!M49/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <f>ROUND(B49*helper!Q49,0)</f>
+        <v>155683</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="2">
+        <v>48</v>
+      </c>
+      <c r="B50" s="30">
+        <v>149758</v>
+      </c>
+      <c r="C50" s="3">
+        <f t="shared" si="0"/>
+        <v>10232</v>
+      </c>
+      <c r="D50">
+        <f>ROUND(helper!M50/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <f>ROUND(helper!M50/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <f>ROUND(B50*helper!Q50,0)</f>
+        <v>139526</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="2">
+        <v>49</v>
+      </c>
+      <c r="B51" s="30">
+        <v>150679</v>
+      </c>
+      <c r="C51" s="3">
+        <f t="shared" si="0"/>
+        <v>10283</v>
+      </c>
+      <c r="D51">
+        <f>ROUND(helper!M51/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <f>ROUND(helper!M51/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <f>ROUND(B51*helper!Q51,0)</f>
+        <v>140396</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="2">
+        <v>50</v>
+      </c>
+      <c r="B52" s="30">
+        <v>154879</v>
+      </c>
+      <c r="C52" s="3">
+        <f t="shared" si="0"/>
+        <v>10557</v>
+      </c>
+      <c r="D52">
+        <f>ROUND(helper!M52/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <f>ROUND(helper!M52/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <f>ROUND(B52*helper!Q52,0)</f>
+        <v>144322</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="2">
+        <v>51</v>
+      </c>
+      <c r="B53" s="30">
+        <v>146276</v>
+      </c>
+      <c r="C53" s="3">
+        <f t="shared" si="0"/>
+        <v>9967</v>
+      </c>
+      <c r="D53">
+        <f>ROUND(helper!M53/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <f>ROUND(helper!M53/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <f>ROUND(B53*helper!Q53,0)</f>
+        <v>136309</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="2">
+        <v>52</v>
+      </c>
+      <c r="B54" s="30">
+        <v>143578</v>
+      </c>
+      <c r="C54" s="3">
+        <f t="shared" si="0"/>
+        <v>9781</v>
+      </c>
+      <c r="D54">
+        <f>ROUND(helper!M54/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <f>ROUND(helper!M54/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <f>ROUND(B54*helper!Q54,0)</f>
+        <v>133797</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="2">
+        <v>53</v>
+      </c>
+      <c r="B55" s="30">
+        <v>137180</v>
+      </c>
+      <c r="C55" s="3">
+        <f t="shared" si="0"/>
+        <v>9342</v>
+      </c>
+      <c r="D55">
+        <f>ROUND(helper!M55/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <f>ROUND(helper!M55/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <f>ROUND(B55*helper!Q55,0)</f>
+        <v>127838</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="2">
+        <v>54</v>
+      </c>
+      <c r="B56" s="30">
+        <v>120058</v>
+      </c>
+      <c r="C56" s="3">
+        <f t="shared" si="0"/>
+        <v>8174</v>
+      </c>
+      <c r="D56">
+        <f>ROUND(helper!M56/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <f>ROUND(helper!M56/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <f>ROUND(B56*helper!Q56,0)</f>
+        <v>111884</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="2">
+        <v>55</v>
+      </c>
+      <c r="B57" s="30">
+        <v>117801</v>
+      </c>
+      <c r="C57" s="3">
+        <f t="shared" si="0"/>
+        <v>8019</v>
+      </c>
+      <c r="D57">
+        <f>ROUND(helper!M57/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <f>ROUND(helper!M57/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <f>ROUND(B57*helper!Q57,0)</f>
+        <v>109782</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="2">
+        <v>56</v>
+      </c>
+      <c r="B58" s="30">
+        <v>132714</v>
+      </c>
+      <c r="C58" s="3">
+        <f t="shared" si="0"/>
+        <v>9032</v>
+      </c>
+      <c r="D58">
+        <f>ROUND(helper!M58/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <f>ROUND(helper!M58/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <f>ROUND(B58*helper!Q58,0)</f>
+        <v>123682</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="2">
+        <v>57</v>
+      </c>
+      <c r="B59" s="30">
+        <v>121511</v>
+      </c>
+      <c r="C59" s="3">
+        <f t="shared" si="0"/>
+        <v>8268</v>
+      </c>
+      <c r="D59">
+        <f>ROUND(helper!M59/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <f>ROUND(helper!M59/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <f>ROUND(B59*helper!Q59,0)</f>
+        <v>113243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="2">
+        <v>58</v>
+      </c>
+      <c r="B60" s="30">
+        <v>123909</v>
+      </c>
+      <c r="C60" s="3">
+        <f t="shared" si="0"/>
+        <v>8429</v>
+      </c>
+      <c r="D60">
+        <f>ROUND(helper!M60/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <f>ROUND(helper!M60/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <f>ROUND(B60*helper!Q60,0)</f>
+        <v>115480</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="2">
+        <v>59</v>
+      </c>
+      <c r="B61" s="30">
+        <v>114481</v>
+      </c>
+      <c r="C61" s="3">
+        <f t="shared" si="0"/>
+        <v>7786</v>
+      </c>
+      <c r="D61">
+        <f>ROUND(helper!M61/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <f>ROUND(helper!M61/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <f>ROUND(B61*helper!Q61,0)</f>
+        <v>106695</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="2">
+        <v>60</v>
+      </c>
+      <c r="B62" s="30">
+        <v>117860</v>
+      </c>
+      <c r="C62" s="3">
+        <f t="shared" si="0"/>
+        <v>8013</v>
+      </c>
+      <c r="D62">
+        <f>ROUND(helper!M62/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <f>ROUND(helper!M62/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <f>ROUND(B62*helper!Q62,0)</f>
+        <v>109847</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="2">
+        <v>61</v>
+      </c>
+      <c r="B63" s="30">
+        <v>108190</v>
+      </c>
+      <c r="C63" s="3">
+        <f t="shared" si="0"/>
+        <v>7355</v>
+      </c>
+      <c r="D63">
+        <f>ROUND(helper!M63/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <f>ROUND(helper!M63/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <f>ROUND(B63*helper!Q63,0)</f>
+        <v>100835</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="2">
+        <v>62</v>
+      </c>
+      <c r="B64" s="30">
+        <v>106387</v>
+      </c>
+      <c r="C64" s="3">
+        <f t="shared" si="0"/>
+        <v>7231</v>
+      </c>
+      <c r="D64">
+        <f>ROUND(helper!M64/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <f>ROUND(helper!M64/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <f>ROUND(B64*helper!Q64,0)</f>
+        <v>99156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="2">
+        <v>63</v>
+      </c>
+      <c r="B65" s="30">
+        <v>102165</v>
+      </c>
+      <c r="C65" s="3">
+        <f t="shared" si="0"/>
+        <v>6943</v>
+      </c>
+      <c r="D65">
+        <f>ROUND(helper!M65/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <f>ROUND(helper!M65/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <f>ROUND(B65*helper!Q65,0)</f>
+        <v>95222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="2">
+        <v>64</v>
+      </c>
+      <c r="B66" s="30">
+        <v>99642</v>
+      </c>
+      <c r="C66" s="3">
+        <f t="shared" si="0"/>
+        <v>6771</v>
+      </c>
+      <c r="D66">
+        <f>ROUND(helper!M66/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <f>ROUND(helper!M66/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <f>ROUND(B66*helper!Q66,0)</f>
+        <v>92871</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="30">
+        <v>1544980</v>
+      </c>
+      <c r="C67" s="3">
+        <f t="shared" si="0"/>
+        <v>104964</v>
+      </c>
+      <c r="D67">
+        <f>ROUND(helper!M67/26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <f>ROUND(helper!M67/52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <f>ROUND(B67*helper!Q67,0)</f>
+        <v>1440016</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" s="3">
+        <f>SUM(B2:B67)</f>
+        <v>10200298</v>
+      </c>
+      <c r="C68" s="3">
+        <f t="shared" ref="C68:F68" si="1">SUM(C2:C67)</f>
+        <v>1222086</v>
+      </c>
+      <c r="D68" s="3">
+        <f t="shared" si="1"/>
+        <v>3521</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" si="1"/>
+        <v>1769</v>
+      </c>
+      <c r="F68" s="3">
+        <f t="shared" si="1"/>
+        <v>8978212</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="2"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="2"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="2"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="2"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="2"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="2"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="2"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="2"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="2"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="2"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="2"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="2"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="2"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="2"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="2"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="2"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="2"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="2"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2"/>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2"/>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F550EE92-E1DE-4EEB-85ED-79A00D3FE3F5}">
   <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2549,7 +2678,7 @@
         <v>1367.5691393066634</v>
       </c>
       <c r="N2">
-        <f>M2/B2</f>
+        <f t="shared" ref="N2:N33" si="0">M2/B2</f>
         <v>1.5491618968561402E-2</v>
       </c>
       <c r="O2">
@@ -2607,11 +2736,11 @@
         <v>3.052003827820492E-2</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M66" si="0">K3*(1+L$70*L3)</f>
+        <f t="shared" ref="M3:M66" si="1">K3*(1+L$70*L3)</f>
         <v>2874.960280865072</v>
       </c>
       <c r="N3">
-        <f>M3/B3</f>
+        <f t="shared" si="0"/>
         <v>3.1508485827726446E-2</v>
       </c>
       <c r="O3">
@@ -2669,23 +2798,23 @@
         <v>9.156011483461475E-2</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6203.2207587340217</v>
       </c>
       <c r="N4">
-        <f>M4/B4</f>
+        <f t="shared" si="0"/>
         <v>6.3359591019192293E-2</v>
       </c>
       <c r="O4">
-        <f t="shared" ref="O4:O67" si="1">O3+N4</f>
+        <f t="shared" ref="O4:O67" si="2">O3+N4</f>
         <v>0.11035969581548014</v>
       </c>
       <c r="P4">
-        <f t="shared" ref="P4:P67" si="2">P3+M4</f>
+        <f t="shared" ref="P4:P67" si="3">P3+M4</f>
         <v>10445.750178905757</v>
       </c>
       <c r="Q4">
-        <f t="shared" ref="Q4:Q67" si="3">O3</f>
+        <f t="shared" ref="Q4:Q67" si="4">O3</f>
         <v>4.7000104796287849E-2</v>
       </c>
     </row>
@@ -2731,23 +2860,23 @@
         <v>0.1700402132642844</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18030.930285189097</v>
       </c>
       <c r="N5">
-        <f>M5/B5</f>
+        <f t="shared" si="0"/>
         <v>0.18118624427417798</v>
       </c>
       <c r="O5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.29154594008965812</v>
       </c>
       <c r="P5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28476.680464094854</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.11035969581548014</v>
       </c>
     </row>
@@ -2793,23 +2922,23 @@
         <v>0.21862313133979486</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23206.303316161731</v>
       </c>
       <c r="N6">
-        <f>M6/B6</f>
+        <f t="shared" si="0"/>
         <v>0.23607152770199721</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5276174677916553</v>
       </c>
       <c r="P6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>51682.983780256589</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29154594008965812</v>
       </c>
     </row>
@@ -2855,23 +2984,23 @@
         <v>0.20613038097752076</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18706.633889298133</v>
       </c>
       <c r="N7">
-        <f>M7/B7</f>
+        <f t="shared" si="0"/>
         <v>0.1867992160140812</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.71441668380573653</v>
       </c>
       <c r="P7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70389.617669554718</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.5276174677916553</v>
       </c>
     </row>
@@ -2917,23 +3046,23 @@
         <v>0.14723598641251517</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10544.396130617142</v>
       </c>
       <c r="N8">
-        <f>M8/B8</f>
+        <f t="shared" si="0"/>
         <v>0.1078401698809256</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.82225685368666213</v>
       </c>
       <c r="P8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80934.013800171859</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.71441668380573653</v>
       </c>
     </row>
@@ -2979,23 +3108,23 @@
         <v>8.1130033329344861E-2</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4312.7933482954086</v>
       </c>
       <c r="N9">
-        <f>M9/B9</f>
+        <f t="shared" si="0"/>
         <v>4.6255747101990694E-2</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.86851260078865278</v>
       </c>
       <c r="P9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>85246.807148467269</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.82225685368666213</v>
       </c>
     </row>
@@ -3041,23 +3170,23 @@
         <v>3.477001428400496E-2</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2046.8997332764973</v>
       </c>
       <c r="N10">
-        <f>M10/B10</f>
+        <f t="shared" si="0"/>
         <v>2.1409069577931965E-2</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.88992167036658476</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>87293.706881743768</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.86851260078865278</v>
       </c>
     </row>
@@ -3103,23 +3232,23 @@
         <v>1.1590004761335005E-2</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1088.3096317322431</v>
       </c>
       <c r="N11">
-        <f>M11/B11</f>
+        <f t="shared" si="0"/>
         <v>1.1386612313840456E-2</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.90130828268042518</v>
       </c>
       <c r="P11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>88382.016513476017</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.88992167036658476</v>
       </c>
     </row>
@@ -3165,23 +3294,23 @@
         <v>2.9802869386289944E-3</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>699.58422282143636</v>
       </c>
       <c r="N12">
-        <f>M12/B12</f>
+        <f t="shared" si="0"/>
         <v>7.1203776330158097E-3</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.90842866031344094</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>89081.600736297449</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.90130828268042518</v>
       </c>
     </row>
@@ -3227,23 +3356,23 @@
         <v>5.8057537765499956E-4</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>487.08427696355398</v>
       </c>
       <c r="N13">
-        <f>M13/B13</f>
+        <f t="shared" si="0"/>
         <v>5.0842808810207928E-3</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.91351294119446169</v>
       </c>
       <c r="P13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>89568.685013260998</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.90842866031344094</v>
       </c>
     </row>
@@ -3289,23 +3418,23 @@
         <v>8.2939339664999767E-5</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>373.08523783517597</v>
       </c>
       <c r="N14">
-        <f>M14/B14</f>
+        <f t="shared" si="0"/>
         <v>3.9498728265859508E-3</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.91746281402104768</v>
       </c>
       <c r="P14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>89941.770251096168</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.91351294119446169</v>
       </c>
     </row>
@@ -3351,23 +3480,23 @@
         <v>8.2027918349999998E-6</v>
       </c>
       <c r="M15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>290.45715932994381</v>
       </c>
       <c r="N15">
-        <f>M15/B15</f>
+        <f t="shared" si="0"/>
         <v>2.957541155392518E-3</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92042035517644016</v>
       </c>
       <c r="P15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90232.227410426116</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.91746281402104768</v>
       </c>
     </row>
@@ -3413,23 +3542,23 @@
         <v>5.0221174499999775E-7</v>
       </c>
       <c r="M16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>236.85857028641124</v>
       </c>
       <c r="N16">
-        <f>M16/B16</f>
+        <f t="shared" si="0"/>
         <v>2.2917878906484816E-3</v>
       </c>
       <c r="O16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9227121430670886</v>
       </c>
       <c r="P16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90469.085980712523</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92042035517644016</v>
       </c>
     </row>
@@ -3475,23 +3604,23 @@
         <v>1.434890699999997E-8</v>
       </c>
       <c r="M17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98.28573120922519</v>
       </c>
       <c r="N17">
-        <f>M17/B17</f>
+        <f t="shared" si="0"/>
         <v>8.7407049792100381E-4</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92358621356500958</v>
       </c>
       <c r="P17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90567.371711921747</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9227121430670886</v>
       </c>
     </row>
@@ -3537,23 +3666,23 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98.285714285714292</v>
       </c>
       <c r="N18">
-        <f>M18/B18</f>
+        <f t="shared" si="0"/>
         <v>8.5580441883665334E-4</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92444201798384629</v>
       </c>
       <c r="P18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90665.657426207457</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92358621356500958</v>
       </c>
     </row>
@@ -3599,23 +3728,23 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98.285714285714292</v>
       </c>
       <c r="N19">
-        <f>M19/B19</f>
+        <f t="shared" si="0"/>
         <v>8.1896572247537158E-4</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9252609837063217</v>
       </c>
       <c r="P19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90763.943140493167</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92444201798384629</v>
       </c>
     </row>
@@ -3661,23 +3790,23 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98.285714285714292</v>
       </c>
       <c r="N20">
-        <f>M20/B20</f>
+        <f t="shared" si="0"/>
         <v>8.1543253480996156E-4</v>
       </c>
       <c r="O20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92607641624113168</v>
       </c>
       <c r="P20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90862.228854778878</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9252609837063217</v>
       </c>
     </row>
@@ -3723,23 +3852,23 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98.285714285714292</v>
       </c>
       <c r="N21">
-        <f>M21/B21</f>
+        <f t="shared" si="0"/>
         <v>7.8191947593210943E-4</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92685833571706377</v>
       </c>
       <c r="P21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90960.514569064588</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92607641624113168</v>
       </c>
     </row>
@@ -3785,23 +3914,23 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N22">
-        <f>M22/B22</f>
+        <f t="shared" si="0"/>
         <v>2.2520727040816323E-4</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92708354298747198</v>
       </c>
       <c r="P22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90989.57171192173</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92685833571706377</v>
       </c>
     </row>
@@ -3847,23 +3976,23 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N23">
-        <f>M23/B23</f>
+        <f t="shared" si="0"/>
         <v>2.3228618022849465E-4</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9273158291677005</v>
       </c>
       <c r="P23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91018.628854778872</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92708354298747198</v>
       </c>
     </row>
@@ -3909,23 +4038,23 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N24">
-        <f>M24/B24</f>
+        <f t="shared" si="0"/>
         <v>2.3769207307453643E-4</v>
       </c>
       <c r="O24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92755352124077506</v>
       </c>
       <c r="P24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91047.685997636014</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9273158291677005</v>
       </c>
     </row>
@@ -3971,23 +4100,23 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N25">
-        <f>M25/B25</f>
+        <f t="shared" si="0"/>
         <v>2.3986612781303176E-4</v>
       </c>
       <c r="O25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92779338736858807</v>
       </c>
       <c r="P25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91076.743140493156</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92755352124077506</v>
       </c>
     </row>
@@ -4033,23 +4162,23 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N26">
-        <f>M26/B26</f>
+        <f t="shared" si="0"/>
         <v>2.4067274777519695E-4</v>
       </c>
       <c r="O26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92803406011636325</v>
       </c>
       <c r="P26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91105.800283350298</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92779338736858807</v>
       </c>
     </row>
@@ -4095,23 +4224,23 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N27">
-        <f>M27/B27</f>
+        <f t="shared" si="0"/>
         <v>2.3613326553499159E-4</v>
       </c>
       <c r="O27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9282701933818982</v>
       </c>
       <c r="P27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91134.85742620744</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92803406011636325</v>
       </c>
     </row>
@@ -4157,23 +4286,23 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N28">
-        <f>M28/B28</f>
+        <f t="shared" si="0"/>
         <v>2.3924204731911287E-4</v>
       </c>
       <c r="O28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92850943542921727</v>
       </c>
       <c r="P28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91163.914569064582</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9282701933818982</v>
       </c>
     </row>
@@ -4219,23 +4348,23 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N29">
-        <f>M29/B29</f>
+        <f t="shared" si="0"/>
         <v>2.468515504680349E-4</v>
       </c>
       <c r="O29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92875628697968526</v>
       </c>
       <c r="P29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91192.971711921724</v>
       </c>
       <c r="Q29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92850943542921727</v>
       </c>
     </row>
@@ -4281,23 +4410,23 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N30">
-        <f>M30/B30</f>
+        <f t="shared" si="0"/>
         <v>2.3984236908604017E-4</v>
       </c>
       <c r="O30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92899612934877129</v>
       </c>
       <c r="P30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91222.028854778866</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92875628697968526</v>
       </c>
     </row>
@@ -4343,23 +4472,23 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.057142857142853</v>
       </c>
       <c r="N31">
-        <f>M31/B31</f>
+        <f t="shared" si="0"/>
         <v>2.2713314200846442E-4</v>
       </c>
       <c r="O31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9292232624907798</v>
       </c>
       <c r="P31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91251.085997636008</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92899612934877129</v>
       </c>
     </row>
@@ -4405,23 +4534,23 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N32">
-        <f>M32/B32</f>
+        <f t="shared" si="0"/>
         <v>2.1396564910880554E-4</v>
       </c>
       <c r="O32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9294372281398886</v>
       </c>
       <c r="P32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91280.500283350295</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9292232624907798</v>
       </c>
     </row>
@@ -4467,23 +4596,23 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N33">
-        <f>M33/B33</f>
+        <f t="shared" si="0"/>
         <v>2.0265309215745329E-4</v>
       </c>
       <c r="O33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92963988123204611</v>
       </c>
       <c r="P33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91309.914569064582</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9294372281398886</v>
       </c>
     </row>
@@ -4529,23 +4658,23 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N34">
-        <f>M34/B34</f>
+        <f t="shared" ref="N34:N65" si="5">M34/B34</f>
         <v>1.9378148713880081E-4</v>
       </c>
       <c r="O34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.92983366271918488</v>
       </c>
       <c r="P34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91339.328854778869</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92963988123204611</v>
       </c>
     </row>
@@ -4591,23 +4720,23 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N35">
-        <f>M35/B35</f>
+        <f t="shared" si="5"/>
         <v>1.818626658646691E-4</v>
       </c>
       <c r="O35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9300155253850495</v>
       </c>
       <c r="P35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91368.743140493156</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.92983366271918488</v>
       </c>
     </row>
@@ -4653,23 +4782,23 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N36">
-        <f>M36/B36</f>
+        <f t="shared" si="5"/>
         <v>1.7387515274243931E-4</v>
       </c>
       <c r="O36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93018940053779198</v>
       </c>
       <c r="P36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91398.157426207443</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9300155253850495</v>
       </c>
     </row>
@@ -4715,23 +4844,23 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N37">
-        <f>M37/B37</f>
+        <f t="shared" si="5"/>
         <v>1.6703646165016448E-4</v>
       </c>
       <c r="O37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93035643699944215</v>
       </c>
       <c r="P37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91427.57171192173</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93018940053779198</v>
       </c>
     </row>
@@ -4777,23 +4906,23 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N38">
-        <f>M38/B38</f>
+        <f t="shared" si="5"/>
         <v>1.5946678149720642E-4</v>
       </c>
       <c r="O38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9305159037809394</v>
       </c>
       <c r="P38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91456.985997636017</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93035643699944215</v>
       </c>
     </row>
@@ -4839,23 +4968,23 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N39">
-        <f>M39/B39</f>
+        <f t="shared" si="5"/>
         <v>1.7803641142926318E-4</v>
       </c>
       <c r="O39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93069394019236862</v>
       </c>
       <c r="P39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91486.400283350304</v>
       </c>
       <c r="Q39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9305159037809394</v>
       </c>
     </row>
@@ -4901,23 +5030,23 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N40">
-        <f>M40/B40</f>
+        <f t="shared" si="5"/>
         <v>1.9993261134906447E-4</v>
       </c>
       <c r="O40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93089387280371771</v>
       </c>
       <c r="P40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91515.814569064591</v>
       </c>
       <c r="Q40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93069394019236862</v>
       </c>
     </row>
@@ -4963,23 +5092,23 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29.414285714285715</v>
       </c>
       <c r="N41">
-        <f>M41/B41</f>
+        <f t="shared" si="5"/>
         <v>2.0611085140098321E-4</v>
       </c>
       <c r="O41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9310999836551187</v>
       </c>
       <c r="P41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91545.228854778878</v>
       </c>
       <c r="Q41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93089387280371771</v>
       </c>
     </row>
@@ -5025,23 +5154,23 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N42">
-        <f>M42/B42</f>
+        <f t="shared" si="5"/>
         <v>6.8627142440913142E-5</v>
       </c>
       <c r="O42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93116861079755964</v>
       </c>
       <c r="P42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91554.885997636025</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.9310999836551187</v>
       </c>
     </row>
@@ -5087,23 +5216,23 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N43">
-        <f>M43/B43</f>
+        <f t="shared" si="5"/>
         <v>6.5931665145166704E-5</v>
       </c>
       <c r="O43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93123454246270476</v>
       </c>
       <c r="P43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91564.543140493173</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93116861079755964</v>
       </c>
     </row>
@@ -5149,23 +5278,23 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N44">
-        <f>M44/B44</f>
+        <f t="shared" si="5"/>
         <v>6.6746446442888342E-5</v>
       </c>
       <c r="O44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93130128890914765</v>
       </c>
       <c r="P44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91574.200283350321</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93123454246270476</v>
       </c>
     </row>
@@ -5211,23 +5340,23 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N45">
-        <f>M45/B45</f>
+        <f t="shared" si="5"/>
         <v>6.5525908420757746E-5</v>
       </c>
       <c r="O45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93136681481756844</v>
       </c>
       <c r="P45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91583.857426207469</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93130128890914765</v>
       </c>
     </row>
@@ -5273,23 +5402,23 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N46">
-        <f>M46/B46</f>
+        <f t="shared" si="5"/>
         <v>7.1393191666429038E-5</v>
       </c>
       <c r="O46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93143820800923482</v>
       </c>
       <c r="P46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91593.514569064617</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93136681481756844</v>
       </c>
     </row>
@@ -5335,23 +5464,23 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N47">
-        <f>M47/B47</f>
+        <f t="shared" si="5"/>
         <v>7.7400798739603563E-5</v>
       </c>
       <c r="O47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93151560880797446</v>
       </c>
       <c r="P47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91603.171711921765</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93143820800923482</v>
       </c>
     </row>
@@ -5397,23 +5526,23 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N48">
-        <f>M48/B48</f>
+        <f t="shared" si="5"/>
         <v>7.9390525046183909E-5</v>
       </c>
       <c r="O48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93159499933302059</v>
       </c>
       <c r="P48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91612.828854778913</v>
       </c>
       <c r="Q48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93151560880797446</v>
       </c>
     </row>
@@ -5459,23 +5588,23 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N49">
-        <f>M49/B49</f>
+        <f t="shared" si="5"/>
         <v>8.0401149403413948E-5</v>
       </c>
       <c r="O49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93167540048242403</v>
       </c>
       <c r="P49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91622.48599763606</v>
       </c>
       <c r="Q49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93159499933302059</v>
       </c>
     </row>
@@ -5521,23 +5650,23 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N50">
-        <f>M50/B50</f>
+        <f t="shared" si="5"/>
         <v>8.2136721189573001E-5</v>
       </c>
       <c r="O50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93175753720361365</v>
       </c>
       <c r="P50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91632.143140493208</v>
       </c>
       <c r="Q50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93167540048242403</v>
       </c>
     </row>
@@ -5583,23 +5712,23 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.6571428571428566</v>
       </c>
       <c r="N51">
-        <f>M51/B51</f>
+        <f t="shared" si="5"/>
         <v>8.2134625455172839E-5</v>
       </c>
       <c r="O51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93183967182906879</v>
       </c>
       <c r="P51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91641.800283350356</v>
       </c>
       <c r="Q51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93175753720361365</v>
       </c>
     </row>
@@ -5646,23 +5775,23 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N52">
-        <f>M52/B52</f>
+        <f t="shared" si="5"/>
         <v>1.9471510745839993E-5</v>
       </c>
       <c r="O52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93185914333981468</v>
       </c>
       <c r="P52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91644.20028335035</v>
       </c>
       <c r="Q52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93183967182906879</v>
       </c>
     </row>
@@ -5709,23 +5838,23 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N53">
-        <f>M53/B53</f>
+        <f t="shared" si="5"/>
         <v>1.8696102641603501E-5</v>
       </c>
       <c r="O53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93187783944245628</v>
       </c>
       <c r="P53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91646.600283350344</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93185914333981468</v>
       </c>
     </row>
@@ -5772,23 +5901,23 @@
         <v>0</v>
       </c>
       <c r="M54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N54">
-        <f>M54/B54</f>
+        <f t="shared" si="5"/>
         <v>1.8293240647580719E-5</v>
       </c>
       <c r="O54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93189613268310389</v>
       </c>
       <c r="P54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91649.000283350339</v>
       </c>
       <c r="Q54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93187783944245628</v>
       </c>
     </row>
@@ -5835,23 +5964,23 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N55">
-        <f>M55/B55</f>
+        <f t="shared" si="5"/>
         <v>1.7862857908408196E-5</v>
       </c>
       <c r="O55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93191399554101229</v>
       </c>
       <c r="P55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91651.400283350333</v>
       </c>
       <c r="Q55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93189613268310389</v>
       </c>
     </row>
@@ -5898,23 +6027,23 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N56">
-        <f>M56/B56</f>
+        <f t="shared" si="5"/>
         <v>1.7094991167587895E-5</v>
       </c>
       <c r="O56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93193109053217993</v>
       </c>
       <c r="P56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91653.800283350327</v>
       </c>
       <c r="Q56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93191399554101229</v>
       </c>
     </row>
@@ -5961,23 +6090,23 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N57">
-        <f>M57/B57</f>
+        <f t="shared" si="5"/>
         <v>1.5362949686339778E-5</v>
       </c>
       <c r="O57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93194645348186622</v>
       </c>
       <c r="P57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91656.200283350321</v>
       </c>
       <c r="Q57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93193109053217993</v>
       </c>
     </row>
@@ -6024,23 +6153,23 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N58">
-        <f>M58/B58</f>
+        <f t="shared" si="5"/>
         <v>1.4229811454998221E-5</v>
       </c>
       <c r="O58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93196068329332127</v>
       </c>
       <c r="P58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91658.600283350315</v>
       </c>
       <c r="Q58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93194645348186622</v>
       </c>
     </row>
@@ -6087,23 +6216,23 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N59">
-        <f>M59/B59</f>
+        <f t="shared" si="5"/>
         <v>1.4275432575347517E-5</v>
       </c>
       <c r="O59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93197495872589664</v>
       </c>
       <c r="P59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91661.000283350309</v>
       </c>
       <c r="Q59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93196068329332127</v>
       </c>
     </row>
@@ -6150,23 +6279,23 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N60">
-        <f>M60/B60</f>
+        <f t="shared" si="5"/>
         <v>1.5715651479235695E-5</v>
       </c>
       <c r="O60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93199067437737593</v>
       </c>
       <c r="P60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91663.400283350304</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93197495872589664</v>
       </c>
     </row>
@@ -6213,23 +6342,23 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
       <c r="N61">
-        <f>M61/B61</f>
+        <f t="shared" si="5"/>
         <v>1.7725782150137376E-5</v>
       </c>
       <c r="O61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93200840015952602</v>
       </c>
       <c r="P61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91665.800283350298</v>
       </c>
       <c r="Q61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93199067437737593</v>
       </c>
     </row>
@@ -6275,23 +6404,23 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="N62">
-        <f>M62/B62</f>
+        <f t="shared" si="5"/>
         <v>9.9036891752677335E-6</v>
       </c>
       <c r="O62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93201830384870132</v>
       </c>
       <c r="P62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91667.185997636014</v>
       </c>
       <c r="Q62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93200840015952602</v>
       </c>
     </row>
@@ -6337,23 +6466,23 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="N63">
-        <f>M63/B63</f>
+        <f t="shared" si="5"/>
         <v>9.978859220928859E-6</v>
       </c>
       <c r="O63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93202828270792226</v>
       </c>
       <c r="P63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91668.57171192173</v>
       </c>
       <c r="Q63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93201830384870132</v>
       </c>
     </row>
@@ -6399,23 +6528,23 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="N64">
-        <f>M64/B64</f>
+        <f t="shared" si="5"/>
         <v>1.0690672553516737E-5</v>
       </c>
       <c r="O64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93203897338047581</v>
       </c>
       <c r="P64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91669.957426207446</v>
       </c>
       <c r="Q64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93202828270792226</v>
       </c>
     </row>
@@ -6461,23 +6590,23 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="N65">
-        <f>M65/B65</f>
+        <f t="shared" si="5"/>
         <v>1.0989969669949686E-5</v>
       </c>
       <c r="O65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93204996335014578</v>
       </c>
       <c r="P65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91671.343140493162</v>
       </c>
       <c r="Q65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93203897338047581</v>
       </c>
     </row>
@@ -6523,23 +6652,23 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3857142857142859</v>
       </c>
       <c r="N66">
-        <f>M66/B66</f>
+        <f t="shared" ref="N66:N67" si="6">M66/B66</f>
         <v>1.1596032483236562E-5</v>
       </c>
       <c r="O66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93206155938262902</v>
       </c>
       <c r="P66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91672.728854778878</v>
       </c>
       <c r="Q66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93204996335014578</v>
       </c>
     </row>
@@ -6585,23 +6714,23 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <f t="shared" ref="M67" si="4">K67*(1+L$70*L67)</f>
+        <f t="shared" ref="M67" si="7">K67*(1+L$70*L67)</f>
         <v>6.9285714285714288</v>
       </c>
       <c r="N67">
-        <f>M67/B67</f>
+        <f t="shared" si="6"/>
         <v>4.1312317714721841E-6</v>
       </c>
       <c r="O67">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93206569061440048</v>
       </c>
       <c r="P67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91679.657426207443</v>
       </c>
       <c r="Q67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93206155938262902</v>
       </c>
     </row>
@@ -6614,31 +6743,31 @@
         <v>40389.000000000022</v>
       </c>
       <c r="E68">
-        <f t="shared" ref="E68:K68" si="5">SUM(E2:E67)</f>
+        <f t="shared" ref="E68:K68" si="8">SUM(E2:E67)</f>
         <v>33453.999999999935</v>
       </c>
       <c r="F68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>34598.000000000015</v>
       </c>
       <c r="G68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>28881.999999999982</v>
       </c>
       <c r="H68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>41620</v>
       </c>
       <c r="I68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>37843.000000000044</v>
       </c>
       <c r="J68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>33391.999999999942</v>
       </c>
       <c r="K68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>35739.714285714304</v>
       </c>
       <c r="L68">
@@ -6646,7 +6775,7 @@
         <v>0.99999999999999845</v>
       </c>
       <c r="M68">
-        <f t="shared" ref="M68" si="6">SUM(M2:M67)</f>
+        <f t="shared" ref="M68" si="9">SUM(M2:M67)</f>
         <v>91679.657426207443</v>
       </c>
     </row>
@@ -6663,7 +6792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAE0496C-68E6-4045-ACAB-47097B39FC40}">
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.5"/>

--- a/resources/number_of_susceptibles_hun.xlsx
+++ b/resources/number_of_susceptibles_hun.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80D16D0-CFF4-4DB4-810E-16405FE436E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E517314-803F-49B4-B0C9-349B13EB6E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="1620" windowWidth="18880" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="490" yWindow="810" windowWidth="18880" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="s0" sheetId="4" r:id="rId1"/>
-    <sheet name="compartments" sheetId="1" r:id="rId2"/>
-    <sheet name="helper" sheetId="2" r:id="rId3"/>
-    <sheet name="Varicella" sheetId="3" r:id="rId4"/>
+    <sheet name="s011" sheetId="5" r:id="rId2"/>
+    <sheet name="s016" sheetId="6" r:id="rId3"/>
+    <sheet name="compartments" sheetId="1" r:id="rId4"/>
+    <sheet name="helper" sheetId="2" r:id="rId5"/>
+    <sheet name="Varicella" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>65+</t>
   </si>
@@ -136,6 +138,9 @@
   </si>
   <si>
     <t>s0</t>
+  </si>
+  <si>
+    <t>15+</t>
   </si>
 </sst>
 </file>
@@ -734,7 +739,8 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>96676</v>
+        <f>ROUND(96676*(1/3),0)</f>
+        <v>32225</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -839,6 +845,274 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD1CFB3-E93D-4818-BB3C-3D956D7E5344}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>s0!B2</f>
+        <v>32225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>s0!B3</f>
+        <v>91425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>s0!B4</f>
+        <v>90914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>s0!B5</f>
+        <v>87137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>s0!B6</f>
+        <v>73581</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>s0!B7</f>
+        <v>52050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>s0!B8</f>
+        <v>32160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>s0!B9</f>
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>s0!B10</f>
+        <v>15711</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>s0!B11</f>
+        <v>13722</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <f>SUM(s0!B12:B14)</f>
+        <v>8404436</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CDD3713-B550-4817-A85F-404063882CAD}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>s0!B2</f>
+        <v>32225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>s0!B3</f>
+        <v>91425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>s0!B4</f>
+        <v>90914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>s0!B5</f>
+        <v>87137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>s0!B6</f>
+        <v>73581</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>s0!B7</f>
+        <v>52050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>s0!B8</f>
+        <v>32160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>s0!B9</f>
+        <v>20400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>s0!B10</f>
+        <v>15711</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>s0!B11</f>
+        <v>13722</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>12351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>11185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10648</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>10234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <f>SUM(s0!B13:B14)</f>
+        <v>8349741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2567,7 +2841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F550EE92-E1DE-4EEB-85ED-79A00D3FE3F5}">
   <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -6792,7 +7066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAE0496C-68E6-4045-ACAB-47097B39FC40}">
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
